--- a/public/files/RFPilot schedule-example-sheet.xlsx
+++ b/public/files/RFPilot schedule-example-sheet.xlsx
@@ -326,6 +326,120 @@
         <x:v>Special requirements</x:v>
       </x:c>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="0" t="str">
+        <x:v>2027-03-10</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="str">
+        <x:v>Wednesday</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="str">
+        <x:v>9:00 AM</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="str">
+        <x:v>11:30 AM</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="str">
+        <x:v>Opening Keynote</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="str">
+        <x:v>Grand Ballroom</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="str">
+        <x:v>Theater</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="str">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="str">
+        <x:v>CEO</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="str">
+        <x:v>Alex</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="str">
+        <x:v>Record keynote</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="0" t="str">
+        <x:v>2027-03-12</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="str">
+        <x:v>Friday</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="str">
+        <x:v>3:00 PM</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="str">
+        <x:v>5:00 PM</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="str">
+        <x:v>Closing General Session</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="str">
+        <x:v>Grand Ballroom</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="str">
+        <x:v>Theater</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="str">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="str">
+        <x:v>CRO</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="str">
+        <x:v>Alex</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="str">
+        <x:v>Same room as the keynote</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="0" t="str">
+        <x:v>2027-03-11</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="str">
+        <x:v>Thursday</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="str">
+        <x:v>9:00 AM</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="str">
+        <x:v>12:00 PM</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="str">
+        <x:v>Breakout A</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="str">
+        <x:v>Salon 1</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="str">
+        <x:v>Classroom</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="str">
+        <x:v>VP Sales</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="str">
+        <x:v>Jamie</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/public/files/RFPilot schedule-example-sheet.xlsx
+++ b/public/files/RFPilot schedule-example-sheet.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="in person schedule" sheetId="1" r:id="Rc8feb0b34eb0481f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Table 1" sheetId="2" r:id="R9be1f4a2fd054d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Virtual schedule" sheetId="3" r:id="R9becd78b41cd47cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="4" r:id="Re687b9ae120d4bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="5" r:id="R2858a4d7e1644439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="in person schedule" sheetId="1" r:id="Ra9942eb23e064602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Table 1" sheetId="2" r:id="R9603e444d85d42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Virtual schedule" sheetId="3" r:id="R0db2e4b953f34e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="4" r:id="R25bf9e999c924a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="5" r:id="R05a6e257ef30423f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -327,118 +327,46 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="0" t="str">
-        <x:v>2027-03-10</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="str">
-        <x:v>Wednesday</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="str">
-        <x:v>9:00 AM</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="str">
-        <x:v>11:30 AM</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="str">
-        <x:v>Opening Keynote</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="str">
-        <x:v>Grand Ballroom</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="str">
-        <x:v>Theater</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="str">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="str">
-        <x:v>CEO</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="str">
-        <x:v>Alex</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="str">
-        <x:v>All</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="str">
-        <x:v>Record keynote</x:v>
-      </x:c>
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="0" t="str">
-        <x:v>2027-03-12</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="str">
-        <x:v>Friday</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="str">
-        <x:v>3:00 PM</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="str">
-        <x:v>5:00 PM</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="str">
-        <x:v>Closing General Session</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="str">
-        <x:v>Grand Ballroom</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="str">
-        <x:v>Theater</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="str">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="str">
-        <x:v>CRO</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="str">
-        <x:v>Alex</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="str">
-        <x:v>All</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="str">
-        <x:v>Same room as the keynote</x:v>
-      </x:c>
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="0" t="str">
-        <x:v>2027-03-11</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="str">
-        <x:v>Thursday</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="str">
-        <x:v>9:00 AM</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="str">
-        <x:v>12:00 PM</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="str">
-        <x:v>Breakout A</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="str">
-        <x:v>Salon 1</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="str">
-        <x:v>Classroom</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="str">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="str">
-        <x:v>VP Sales</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="str">
-        <x:v>Jamie</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="str">
-        <x:v>Advanced</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="str">
-        <x:v/>
-      </x:c>
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
